--- a/Result/profitability/2413.xlsx
+++ b/Result/profitability/2413.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.62</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01374999999999994</v>
+        <v>0.2999999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>14.11125</v>
+        <v>15.135</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.44</v>
       </c>
       <c r="M3" t="n">
-        <v>0.009999999999999946</v>
+        <v>0.2174999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>13.7875</v>
+        <v>14.12375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.44</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03749999999999995</v>
+        <v>0.2537499999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>14.26375</v>
+        <v>14.48375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,13 +1018,13 @@
         <v>0.22</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04624999999999994</v>
+        <v>0.41875</v>
       </c>
       <c r="N5" t="n">
-        <v>14.14625</v>
+        <v>14.945</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
@@ -1036,7 +1036,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.11</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1975</v>
+        <v>0.3462499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>14.84625</v>
+        <v>15.22125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.59</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03749999999999998</v>
+        <v>0.18875</v>
       </c>
       <c r="N7" t="n">
-        <v>14.7125</v>
+        <v>14.85125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.26</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.07875000000000003</v>
+        <v>0.09249999999999994</v>
       </c>
       <c r="N8" t="n">
-        <v>14.51625</v>
+        <v>14.83875</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>0.2</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.02750000000000003</v>
+        <v>-0.02750000000000004</v>
       </c>
       <c r="N10" t="n">
         <v>16.03625</v>
@@ -1772,7 +1772,7 @@
         <v>0.39</v>
       </c>
       <c r="M11" t="n">
-        <v>0.07624999999999997</v>
+        <v>0.07624999999999996</v>
       </c>
       <c r="N11" t="n">
         <v>17.72625</v>
@@ -1899,7 +1899,7 @@
         <v>0.45</v>
       </c>
       <c r="M12" t="n">
-        <v>0.07749999999999997</v>
+        <v>0.07749999999999996</v>
       </c>
       <c r="N12" t="n">
         <v>17.83125</v>
@@ -2026,7 +2026,7 @@
         <v>0.1</v>
       </c>
       <c r="M13" t="n">
-        <v>0.06249999999999997</v>
+        <v>0.06249999999999996</v>
       </c>
       <c r="N13" t="n">
         <v>17.86875</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2413</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>969</v>
+      </c>
+      <c r="D75" t="n">
+        <v>793</v>
+      </c>
+      <c r="E75" t="n">
+        <v>176</v>
+      </c>
+      <c r="F75" t="n">
+        <v>18.16</v>
+      </c>
+      <c r="G75" t="n">
+        <v>46</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>4.73%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>215</v>
+      </c>
+      <c r="J75" t="n">
+        <v>261</v>
+      </c>
+      <c r="K75" t="n">
+        <v>240</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.3262499999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>14.945</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X75" t="n">
+        <v>2.686274509803921</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1655969191270861</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-2.709090909090909</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>6.390000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.5429056924384028</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
